--- a/Methane/Methane_Bio_H2_Brownfield_Patagonien/Datenbank.xlsx
+++ b/Methane/Methane_Bio_H2_Brownfield_Patagonien/Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_Bio_H2_Brownfield_Patagonien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642C458D-24CE-46EB-822D-2CB19610EFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57206E4B-4315-4ECC-8ECF-2568F4DB2B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2405,7 +2405,7 @@
         <v>78</v>
       </c>
       <c r="E51" s="26">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F51" s="25" t="s">
         <v>19</v>
@@ -3918,12 +3918,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="B54:B63"/>
-    <mergeCell ref="B64:B73"/>
-    <mergeCell ref="A74:A83"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B74:B77"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="A84:A109"/>
     <mergeCell ref="A2:A22"/>
@@ -3940,6 +3934,12 @@
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="B103:B107"/>
     <mergeCell ref="A45:A73"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="B54:B63"/>
+    <mergeCell ref="B64:B73"/>
+    <mergeCell ref="A74:A83"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B74:B77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methane/Methane_Bio_H2_Brownfield_Patagonien/Datenbank.xlsx
+++ b/Methane/Methane_Bio_H2_Brownfield_Patagonien/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_Bio_H2_Brownfield_Patagonien\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_Bio_H2_Brownfield_Patagonien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57206E4B-4315-4ECC-8ECF-2568F4DB2B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEFF3CA-6737-402E-BA17-04D889C35FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1019,10 +1019,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1154,41 +1154,41 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1197,8 +1197,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1210,9 +1208,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1243,9 +1238,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1582,10 +1574,10 @@
       <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1602,8 +1594,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="39"/>
-      <c r="B3" s="47"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="44"/>
       <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
@@ -1618,8 +1610,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="39"/>
-      <c r="B4" s="47"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
@@ -1627,15 +1619,15 @@
         <v>26</v>
       </c>
       <c r="E4" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
-      <c r="B5" s="47"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1650,8 +1642,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
-      <c r="B6" s="47"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
@@ -1666,8 +1658,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
-      <c r="B7" s="47"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1682,8 +1674,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
-      <c r="B8" s="50" t="s">
+      <c r="A8" s="37"/>
+      <c r="B8" s="47" t="s">
         <v>243</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -1701,8 +1693,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
-      <c r="B9" s="47"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
@@ -1717,8 +1709,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="39"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
@@ -1733,8 +1725,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="39"/>
-      <c r="B11" s="47"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -1749,8 +1741,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
-      <c r="B12" s="47"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
@@ -1765,8 +1757,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="39"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="6" t="s">
         <v>228</v>
       </c>
@@ -1781,8 +1773,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="39"/>
-      <c r="B14" s="47"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="44"/>
       <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
@@ -1797,8 +1789,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="39"/>
-      <c r="B15" s="51"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="48"/>
       <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
@@ -1813,10 +1805,10 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="39" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -1833,8 +1825,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="40"/>
       <c r="C17" s="6" t="s">
         <v>11</v>
       </c>
@@ -1849,8 +1841,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="40"/>
       <c r="C18" s="6" t="s">
         <v>13</v>
       </c>
@@ -1865,8 +1857,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="6" t="s">
         <v>20</v>
       </c>
@@ -1881,8 +1873,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="40"/>
       <c r="C20" s="6" t="s">
         <v>35</v>
       </c>
@@ -1897,8 +1889,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="40"/>
       <c r="C21" s="6" t="s">
         <v>36</v>
       </c>
@@ -1913,8 +1905,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="39"/>
-      <c r="B22" s="43"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="40"/>
       <c r="C22" s="6" t="s">
         <v>15</v>
       </c>
@@ -1929,8 +1921,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
-      <c r="B23" s="44"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="41"/>
       <c r="C23" s="15" t="s">
         <v>88</v>
       </c>
@@ -1945,8 +1937,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
-      <c r="B24" s="45" t="s">
+      <c r="A24" s="37"/>
+      <c r="B24" s="42" t="s">
         <v>200</v>
       </c>
       <c r="C24" s="13" t="s">
@@ -1963,8 +1955,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
-      <c r="B25" s="47"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="44"/>
       <c r="C25" s="6" t="s">
         <v>21</v>
       </c>
@@ -1980,8 +1972,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="44"/>
       <c r="C26" s="6" t="s">
         <v>16</v>
       </c>
@@ -1996,8 +1988,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="39"/>
-      <c r="B27" s="47"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="44"/>
       <c r="C27" s="6" t="s">
         <v>17</v>
       </c>
@@ -2012,8 +2004,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="39"/>
-      <c r="B28" s="47"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="44"/>
       <c r="C28" s="6" t="s">
         <v>35</v>
       </c>
@@ -2028,8 +2020,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
-      <c r="B29" s="47"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="44"/>
       <c r="C29" s="6" t="s">
         <v>36</v>
       </c>
@@ -2044,8 +2036,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="44"/>
       <c r="C30" s="6" t="s">
         <v>89</v>
       </c>
@@ -2060,8 +2052,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
-      <c r="B31" s="47"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="44"/>
       <c r="C31" s="6" t="s">
         <v>88</v>
       </c>
@@ -2076,8 +2068,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
-      <c r="B32" s="47"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="44"/>
       <c r="C32" s="6" t="s">
         <v>13</v>
       </c>
@@ -2092,8 +2084,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="40"/>
-      <c r="B33" s="48"/>
+      <c r="A33" s="38"/>
+      <c r="B33" s="45"/>
       <c r="C33" s="19" t="s">
         <v>15</v>
       </c>
@@ -2108,7 +2100,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="38" t="s">
+      <c r="A34" s="36" t="s">
         <v>72</v>
       </c>
       <c r="B34" s="32" t="s">
@@ -2128,8 +2120,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="41"/>
-      <c r="B35" s="36" t="s">
+      <c r="A35" s="37"/>
+      <c r="B35" s="34" t="s">
         <v>286</v>
       </c>
       <c r="C35" s="28" t="s">
@@ -2138,7 +2130,7 @@
       <c r="D35" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="E35" s="37">
+      <c r="E35" s="35">
         <v>5</v>
       </c>
       <c r="F35" s="28" t="s">
@@ -2146,7 +2138,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="41"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="30" t="s">
         <v>279</v>
       </c>
@@ -2164,8 +2156,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="39"/>
-      <c r="B37" s="45" t="s">
+      <c r="A37" s="37"/>
+      <c r="B37" s="42" t="s">
         <v>4</v>
       </c>
       <c r="C37" s="13" t="s">
@@ -2182,8 +2174,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
-      <c r="B38" s="43"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="40"/>
       <c r="C38" s="6" t="s">
         <v>10</v>
       </c>
@@ -2198,8 +2190,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="39"/>
-      <c r="B39" s="43"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="40"/>
       <c r="C39" s="6" t="s">
         <v>17</v>
       </c>
@@ -2214,8 +2206,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="39"/>
-      <c r="B40" s="43"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="40"/>
       <c r="C40" s="6" t="s">
         <v>18</v>
       </c>
@@ -2230,8 +2222,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="39"/>
-      <c r="B41" s="43"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="40"/>
       <c r="C41" s="6" t="s">
         <v>13</v>
       </c>
@@ -2246,8 +2238,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="39"/>
-      <c r="B42" s="43"/>
+      <c r="A42" s="37"/>
+      <c r="B42" s="40"/>
       <c r="C42" s="6" t="s">
         <v>68</v>
       </c>
@@ -2262,8 +2254,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
-      <c r="B43" s="44"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="41"/>
       <c r="C43" s="15" t="s">
         <v>15</v>
       </c>
@@ -2278,8 +2270,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="39"/>
-      <c r="B44" s="45" t="s">
+      <c r="A44" s="37"/>
+      <c r="B44" s="42" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="13" t="s">
@@ -2296,8 +2288,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="39"/>
-      <c r="B45" s="43"/>
+      <c r="A45" s="37"/>
+      <c r="B45" s="40"/>
       <c r="C45" s="6" t="s">
         <v>10</v>
       </c>
@@ -2312,8 +2304,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="39"/>
-      <c r="B46" s="43"/>
+      <c r="A46" s="37"/>
+      <c r="B46" s="40"/>
       <c r="C46" s="6" t="s">
         <v>17</v>
       </c>
@@ -2328,8 +2320,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39"/>
-      <c r="B47" s="43"/>
+      <c r="A47" s="37"/>
+      <c r="B47" s="40"/>
       <c r="C47" s="6" t="s">
         <v>18</v>
       </c>
@@ -2344,8 +2336,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
-      <c r="B48" s="43"/>
+      <c r="A48" s="37"/>
+      <c r="B48" s="40"/>
       <c r="C48" s="6" t="s">
         <v>13</v>
       </c>
@@ -2360,8 +2352,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
-      <c r="B49" s="43"/>
+      <c r="A49" s="37"/>
+      <c r="B49" s="40"/>
       <c r="C49" s="6" t="s">
         <v>68</v>
       </c>
@@ -2376,8 +2368,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="40"/>
-      <c r="B50" s="46"/>
+      <c r="A50" s="38"/>
+      <c r="B50" s="43"/>
       <c r="C50" s="19" t="s">
         <v>15</v>
       </c>
@@ -2392,7 +2384,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="38" t="s">
+      <c r="A51" s="36" t="s">
         <v>76</v>
       </c>
       <c r="B51" s="24" t="s">
@@ -2412,7 +2404,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="39"/>
+      <c r="A52" s="37"/>
       <c r="B52" s="27" t="s">
         <v>79</v>
       </c>
@@ -2430,7 +2422,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="40"/>
+      <c r="A53" s="38"/>
       <c r="B53" s="4" t="s">
         <v>276</v>
       </c>
@@ -2501,10 +2493,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -2519,8 +2511,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="39"/>
-      <c r="B3" s="47"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="44"/>
       <c r="C3" s="6" t="s">
         <v>107</v>
       </c>
@@ -2533,8 +2525,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="39"/>
-      <c r="B4" s="47"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="6" t="s">
         <v>84</v>
       </c>
@@ -2547,8 +2539,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
-      <c r="B5" s="47"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="6" t="s">
         <v>138</v>
       </c>
@@ -2561,8 +2553,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
-      <c r="B6" s="47"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="6" t="s">
         <v>141</v>
       </c>
@@ -2575,8 +2567,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
-      <c r="B7" s="47"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="6" t="s">
         <v>155</v>
       </c>
@@ -2589,8 +2581,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
-      <c r="B8" s="47"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="6" t="s">
         <v>195</v>
       </c>
@@ -2603,8 +2595,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
-      <c r="B9" s="47"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="6" t="s">
         <v>167</v>
       </c>
@@ -2617,8 +2609,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="39"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="6" t="s">
         <v>187</v>
       </c>
@@ -2631,13 +2623,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="39"/>
-      <c r="B11" s="47"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="44"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
-      <c r="B12" s="50" t="s">
+      <c r="A12" s="37"/>
+      <c r="B12" s="47" t="s">
         <v>243</v>
       </c>
       <c r="C12" s="13" t="s">
@@ -2652,8 +2644,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="39"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="6" t="s">
         <v>229</v>
       </c>
@@ -2666,8 +2658,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="39"/>
-      <c r="B14" s="47"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="44"/>
       <c r="C14" s="6" t="s">
         <v>139</v>
       </c>
@@ -2680,8 +2672,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="39"/>
-      <c r="B15" s="47"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="44"/>
       <c r="C15" s="6" t="s">
         <v>230</v>
       </c>
@@ -2694,8 +2686,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="39"/>
-      <c r="B16" s="47"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="44"/>
       <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
@@ -2708,8 +2700,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
-      <c r="B17" s="47"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="44"/>
       <c r="C17" s="6" t="s">
         <v>141</v>
       </c>
@@ -2722,8 +2714,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="44"/>
       <c r="C18" s="6" t="s">
         <v>155</v>
       </c>
@@ -2736,8 +2728,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
-      <c r="B19" s="47"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="44"/>
       <c r="C19" s="6" t="s">
         <v>195</v>
       </c>
@@ -2750,8 +2742,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
-      <c r="B20" s="47"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="44"/>
       <c r="C20" s="6" t="s">
         <v>167</v>
       </c>
@@ -2764,8 +2756,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="44"/>
       <c r="C21" s="6" t="s">
         <v>187</v>
       </c>
@@ -2778,18 +2770,18 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="39"/>
-      <c r="B22" s="51"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="48"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
       <c r="F22" s="15"/>
     </row>
     <row r="23" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="39" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -2804,8 +2796,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
-      <c r="B24" s="43"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="40"/>
       <c r="C24" s="6" t="s">
         <v>111</v>
       </c>
@@ -2818,8 +2810,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
-      <c r="B25" s="43"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="40"/>
       <c r="C25" s="6" t="s">
         <v>135</v>
       </c>
@@ -2832,8 +2824,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
-      <c r="B26" s="43"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="40"/>
       <c r="C26" s="6" t="s">
         <v>136</v>
       </c>
@@ -2846,8 +2838,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="39"/>
-      <c r="B27" s="43"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="40"/>
       <c r="C27" s="6" t="s">
         <v>141</v>
       </c>
@@ -2860,8 +2852,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="39"/>
-      <c r="B28" s="43"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="40"/>
       <c r="C28" s="6" t="s">
         <v>155</v>
       </c>
@@ -2874,8 +2866,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
-      <c r="B29" s="43"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="40"/>
       <c r="C29" s="6" t="s">
         <v>195</v>
       </c>
@@ -2888,8 +2880,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
-      <c r="B30" s="43"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="6" t="s">
         <v>167</v>
       </c>
@@ -2902,8 +2894,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
-      <c r="B31" s="43"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="40"/>
       <c r="C31" s="6" t="s">
         <v>187</v>
       </c>
@@ -2916,16 +2908,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
-      <c r="B32" s="44"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="16"/>
       <c r="F32" s="15"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="39"/>
-      <c r="B33" s="45" t="s">
+      <c r="A33" s="37"/>
+      <c r="B33" s="42" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="13" t="s">
@@ -2940,8 +2932,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="39"/>
-      <c r="B34" s="43"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="40"/>
       <c r="C34" s="6" t="s">
         <v>113</v>
       </c>
@@ -2954,8 +2946,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
-      <c r="B35" s="47"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="44"/>
       <c r="C35" s="6" t="s">
         <v>111</v>
       </c>
@@ -2968,8 +2960,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="39"/>
-      <c r="B36" s="47"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="44"/>
       <c r="C36" s="6" t="s">
         <v>107</v>
       </c>
@@ -2982,8 +2974,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="39"/>
-      <c r="B37" s="47"/>
+      <c r="A37" s="37"/>
+      <c r="B37" s="44"/>
       <c r="C37" s="6" t="s">
         <v>126</v>
       </c>
@@ -2996,8 +2988,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
-      <c r="B38" s="47"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="44"/>
       <c r="C38" s="6" t="s">
         <v>127</v>
       </c>
@@ -3010,8 +3002,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="39"/>
-      <c r="B39" s="47"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="44"/>
       <c r="C39" s="6" t="s">
         <v>141</v>
       </c>
@@ -3024,8 +3016,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="39"/>
-      <c r="B40" s="47"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="44"/>
       <c r="C40" s="6" t="s">
         <v>155</v>
       </c>
@@ -3038,8 +3030,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="39"/>
-      <c r="B41" s="47"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="44"/>
       <c r="C41" s="6" t="s">
         <v>195</v>
       </c>
@@ -3052,8 +3044,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="39"/>
-      <c r="B42" s="47"/>
+      <c r="A42" s="37"/>
+      <c r="B42" s="44"/>
       <c r="C42" s="6" t="s">
         <v>167</v>
       </c>
@@ -3066,8 +3058,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
-      <c r="B43" s="47"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="44"/>
       <c r="C43" s="6" t="s">
         <v>187</v>
       </c>
@@ -3080,18 +3072,18 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="40"/>
-      <c r="B44" s="48"/>
+      <c r="A44" s="38"/>
+      <c r="B44" s="45"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
       <c r="E44" s="20"/>
       <c r="F44" s="19"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="38" t="s">
+      <c r="A45" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="49" t="s">
+      <c r="B45" s="46" t="s">
         <v>73</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -3106,30 +3098,30 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="39"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="34" t="s">
+      <c r="A46" s="37"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="34" t="s">
+      <c r="D46" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E46" s="35"/>
-      <c r="F46" s="34" t="s">
+      <c r="E46" s="9"/>
+      <c r="F46" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39"/>
-      <c r="B47" s="51"/>
+      <c r="A47" s="37"/>
+      <c r="B47" s="48"/>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="31"/>
       <c r="F47" s="15"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
-      <c r="B48" s="50" t="s">
+      <c r="A48" s="37"/>
+      <c r="B48" s="47" t="s">
         <v>289</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3144,8 +3136,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
-      <c r="B49" s="52"/>
+      <c r="A49" s="37"/>
+      <c r="B49" s="44"/>
       <c r="C49" s="6" t="s">
         <v>292</v>
       </c>
@@ -3158,16 +3150,16 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
-      <c r="B50" s="51"/>
+      <c r="A50" s="37"/>
+      <c r="B50" s="48"/>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
       <c r="E50" s="31"/>
       <c r="F50" s="15"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="39"/>
-      <c r="B51" s="47" t="s">
+      <c r="A51" s="37"/>
+      <c r="B51" s="44" t="s">
         <v>279</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3182,8 +3174,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="39"/>
-      <c r="B52" s="47"/>
+      <c r="A52" s="37"/>
+      <c r="B52" s="44"/>
       <c r="C52" s="6" t="s">
         <v>284</v>
       </c>
@@ -3196,13 +3188,13 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="39"/>
-      <c r="B53" s="47"/>
+      <c r="A53" s="37"/>
+      <c r="B53" s="44"/>
       <c r="E53" s="9"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="39"/>
-      <c r="B54" s="45" t="s">
+      <c r="A54" s="37"/>
+      <c r="B54" s="42" t="s">
         <v>4</v>
       </c>
       <c r="C54" s="13" t="s">
@@ -3217,8 +3209,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="39"/>
-      <c r="B55" s="43"/>
+      <c r="A55" s="37"/>
+      <c r="B55" s="40"/>
       <c r="C55" s="6" t="s">
         <v>107</v>
       </c>
@@ -3231,8 +3223,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="39"/>
-      <c r="B56" s="43"/>
+      <c r="A56" s="37"/>
+      <c r="B56" s="40"/>
       <c r="C56" s="6" t="s">
         <v>122</v>
       </c>
@@ -3245,8 +3237,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="39"/>
-      <c r="B57" s="43"/>
+      <c r="A57" s="37"/>
+      <c r="B57" s="40"/>
       <c r="C57" s="6" t="s">
         <v>141</v>
       </c>
@@ -3259,8 +3251,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="39"/>
-      <c r="B58" s="43"/>
+      <c r="A58" s="37"/>
+      <c r="B58" s="40"/>
       <c r="C58" s="6" t="s">
         <v>155</v>
       </c>
@@ -3273,8 +3265,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="39"/>
-      <c r="B59" s="43"/>
+      <c r="A59" s="37"/>
+      <c r="B59" s="40"/>
       <c r="C59" s="6" t="s">
         <v>161</v>
       </c>
@@ -3287,8 +3279,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="39"/>
-      <c r="B60" s="43"/>
+      <c r="A60" s="37"/>
+      <c r="B60" s="40"/>
       <c r="C60" s="6" t="s">
         <v>195</v>
       </c>
@@ -3301,8 +3293,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="39"/>
-      <c r="B61" s="43"/>
+      <c r="A61" s="37"/>
+      <c r="B61" s="40"/>
       <c r="C61" s="6" t="s">
         <v>167</v>
       </c>
@@ -3315,8 +3307,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="39"/>
-      <c r="B62" s="43"/>
+      <c r="A62" s="37"/>
+      <c r="B62" s="40"/>
       <c r="C62" s="6" t="s">
         <v>187</v>
       </c>
@@ -3329,12 +3321,12 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="39"/>
-      <c r="B63" s="44"/>
+      <c r="A63" s="37"/>
+      <c r="B63" s="41"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="39"/>
-      <c r="B64" s="45" t="s">
+      <c r="A64" s="37"/>
+      <c r="B64" s="42" t="s">
         <v>5</v>
       </c>
       <c r="C64" s="13" t="s">
@@ -3349,8 +3341,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="39"/>
-      <c r="B65" s="43"/>
+      <c r="A65" s="37"/>
+      <c r="B65" s="40"/>
       <c r="C65" s="6" t="s">
         <v>108</v>
       </c>
@@ -3363,8 +3355,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="39"/>
-      <c r="B66" s="43"/>
+      <c r="A66" s="37"/>
+      <c r="B66" s="40"/>
       <c r="C66" s="6" t="s">
         <v>120</v>
       </c>
@@ -3377,8 +3369,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="39"/>
-      <c r="B67" s="43"/>
+      <c r="A67" s="37"/>
+      <c r="B67" s="40"/>
       <c r="C67" s="6" t="s">
         <v>141</v>
       </c>
@@ -3391,8 +3383,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="39"/>
-      <c r="B68" s="43"/>
+      <c r="A68" s="37"/>
+      <c r="B68" s="40"/>
       <c r="C68" s="6" t="s">
         <v>155</v>
       </c>
@@ -3405,8 +3397,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="39"/>
-      <c r="B69" s="43"/>
+      <c r="A69" s="37"/>
+      <c r="B69" s="40"/>
       <c r="C69" s="6" t="s">
         <v>161</v>
       </c>
@@ -3419,8 +3411,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="39"/>
-      <c r="B70" s="43"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="40"/>
       <c r="C70" s="6" t="s">
         <v>195</v>
       </c>
@@ -3433,8 +3425,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="39"/>
-      <c r="B71" s="43"/>
+      <c r="A71" s="37"/>
+      <c r="B71" s="40"/>
       <c r="C71" s="6" t="s">
         <v>167</v>
       </c>
@@ -3447,8 +3439,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="39"/>
-      <c r="B72" s="43"/>
+      <c r="A72" s="37"/>
+      <c r="B72" s="40"/>
       <c r="C72" s="6" t="s">
         <v>187</v>
       </c>
@@ -3461,14 +3453,14 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="40"/>
-      <c r="B73" s="46"/>
+      <c r="A73" s="38"/>
+      <c r="B73" s="43"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="38" t="s">
+      <c r="A74" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="49" t="s">
+      <c r="B74" s="46" t="s">
         <v>73</v>
       </c>
       <c r="C74" s="7" t="s">
@@ -3483,8 +3475,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="39"/>
-      <c r="B75" s="47"/>
+      <c r="A75" s="37"/>
+      <c r="B75" s="44"/>
       <c r="C75" s="6" t="s">
         <v>227</v>
       </c>
@@ -3497,8 +3489,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="39"/>
-      <c r="B76" s="47"/>
+      <c r="A76" s="37"/>
+      <c r="B76" s="44"/>
       <c r="C76" s="6" t="s">
         <v>150</v>
       </c>
@@ -3511,16 +3503,16 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="39"/>
-      <c r="B77" s="51"/>
+      <c r="A77" s="37"/>
+      <c r="B77" s="48"/>
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
       <c r="E77" s="16"/>
       <c r="F77" s="15"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="39"/>
-      <c r="B78" s="50" t="s">
+      <c r="A78" s="37"/>
+      <c r="B78" s="47" t="s">
         <v>79</v>
       </c>
       <c r="C78" s="13" t="s">
@@ -3535,8 +3527,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="39"/>
-      <c r="B79" s="47"/>
+      <c r="A79" s="37"/>
+      <c r="B79" s="44"/>
       <c r="C79" s="6" t="s">
         <v>151</v>
       </c>
@@ -3549,16 +3541,16 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="39"/>
-      <c r="B80" s="51"/>
+      <c r="A80" s="37"/>
+      <c r="B80" s="48"/>
       <c r="C80" s="15"/>
       <c r="D80" s="15"/>
       <c r="E80" s="16"/>
       <c r="F80" s="15"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="39"/>
-      <c r="B81" s="50" t="s">
+      <c r="A81" s="37"/>
+      <c r="B81" s="47" t="s">
         <v>268</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -3573,8 +3565,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="39"/>
-      <c r="B82" s="47"/>
+      <c r="A82" s="37"/>
+      <c r="B82" s="44"/>
       <c r="C82" s="6" t="s">
         <v>270</v>
       </c>
@@ -3587,18 +3579,18 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="40"/>
-      <c r="B83" s="48"/>
+      <c r="A83" s="38"/>
+      <c r="B83" s="45"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
       <c r="E83" s="20"/>
       <c r="F83" s="19"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="38" t="s">
+      <c r="A84" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="B84" s="49" t="s">
+      <c r="B84" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C84" s="7" t="s">
@@ -3613,8 +3605,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="39"/>
-      <c r="B85" s="47"/>
+      <c r="A85" s="37"/>
+      <c r="B85" s="44"/>
       <c r="C85" s="6" t="s">
         <v>174</v>
       </c>
@@ -3626,16 +3618,16 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="39"/>
-      <c r="B86" s="51"/>
+      <c r="A86" s="37"/>
+      <c r="B86" s="48"/>
       <c r="C86" s="15"/>
       <c r="D86" s="15"/>
       <c r="E86" s="15"/>
       <c r="F86" s="15"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="39"/>
-      <c r="B87" s="50" t="s">
+      <c r="A87" s="37"/>
+      <c r="B87" s="47" t="s">
         <v>183</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -3649,8 +3641,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="39"/>
-      <c r="B88" s="47"/>
+      <c r="A88" s="37"/>
+      <c r="B88" s="44"/>
       <c r="C88" s="6" t="s">
         <v>181</v>
       </c>
@@ -3662,8 +3654,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="39"/>
-      <c r="B89" s="47"/>
+      <c r="A89" s="37"/>
+      <c r="B89" s="44"/>
       <c r="C89" s="6" t="s">
         <v>177</v>
       </c>
@@ -3675,8 +3667,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="39"/>
-      <c r="B90" s="47"/>
+      <c r="A90" s="37"/>
+      <c r="B90" s="44"/>
       <c r="C90" s="6" t="s">
         <v>179</v>
       </c>
@@ -3688,8 +3680,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="39"/>
-      <c r="B91" s="47"/>
+      <c r="A91" s="37"/>
+      <c r="B91" s="44"/>
       <c r="C91" s="6" t="s">
         <v>182</v>
       </c>
@@ -3701,8 +3693,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="39"/>
-      <c r="B92" s="47"/>
+      <c r="A92" s="37"/>
+      <c r="B92" s="44"/>
       <c r="C92" s="6" t="s">
         <v>190</v>
       </c>
@@ -3714,12 +3706,12 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="39"/>
-      <c r="B93" s="47"/>
+      <c r="A93" s="37"/>
+      <c r="B93" s="44"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="39"/>
-      <c r="B94" s="50" t="s">
+      <c r="A94" s="37"/>
+      <c r="B94" s="47" t="s">
         <v>205</v>
       </c>
       <c r="C94" s="13" t="s">
@@ -3734,8 +3726,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="39"/>
-      <c r="B95" s="47"/>
+      <c r="A95" s="37"/>
+      <c r="B95" s="44"/>
       <c r="C95" s="6" t="s">
         <v>203</v>
       </c>
@@ -3747,8 +3739,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="39"/>
-      <c r="B96" s="47"/>
+      <c r="A96" s="37"/>
+      <c r="B96" s="44"/>
       <c r="C96" s="6" t="s">
         <v>214</v>
       </c>
@@ -3760,8 +3752,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="39"/>
-      <c r="B97" s="47"/>
+      <c r="A97" s="37"/>
+      <c r="B97" s="44"/>
       <c r="C97" s="6" t="s">
         <v>204</v>
       </c>
@@ -3773,8 +3765,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="39"/>
-      <c r="B98" s="47"/>
+      <c r="A98" s="37"/>
+      <c r="B98" s="44"/>
       <c r="C98" s="6" t="s">
         <v>216</v>
       </c>
@@ -3786,8 +3778,8 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="39"/>
-      <c r="B99" s="47"/>
+      <c r="A99" s="37"/>
+      <c r="B99" s="44"/>
       <c r="C99" s="6" t="s">
         <v>220</v>
       </c>
@@ -3799,8 +3791,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="39"/>
-      <c r="B100" s="47"/>
+      <c r="A100" s="37"/>
+      <c r="B100" s="44"/>
       <c r="C100" s="6" t="s">
         <v>201</v>
       </c>
@@ -3812,8 +3804,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="39"/>
-      <c r="B101" s="47"/>
+      <c r="A101" s="37"/>
+      <c r="B101" s="44"/>
       <c r="C101" s="6" t="s">
         <v>275</v>
       </c>
@@ -3825,12 +3817,12 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="39"/>
-      <c r="B102" s="47"/>
+      <c r="A102" s="37"/>
+      <c r="B102" s="44"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="39"/>
-      <c r="B103" s="50" t="s">
+      <c r="A103" s="37"/>
+      <c r="B103" s="47" t="s">
         <v>221</v>
       </c>
       <c r="C103" s="13" t="s">
@@ -3845,8 +3837,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="39"/>
-      <c r="B104" s="47"/>
+      <c r="A104" s="37"/>
+      <c r="B104" s="44"/>
       <c r="C104" s="6" t="s">
         <v>224</v>
       </c>
@@ -3858,8 +3850,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="39"/>
-      <c r="B105" s="47"/>
+      <c r="A105" s="37"/>
+      <c r="B105" s="44"/>
       <c r="C105" s="6" t="s">
         <v>232</v>
       </c>
@@ -3871,8 +3863,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="39"/>
-      <c r="B106" s="47"/>
+      <c r="A106" s="37"/>
+      <c r="B106" s="44"/>
       <c r="C106" s="6" t="s">
         <v>234</v>
       </c>
@@ -3884,12 +3876,12 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="39"/>
-      <c r="B107" s="47"/>
+      <c r="A107" s="37"/>
+      <c r="B107" s="44"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="39"/>
-      <c r="B108" s="50" t="s">
+      <c r="A108" s="37"/>
+      <c r="B108" s="47" t="s">
         <v>236</v>
       </c>
       <c r="C108" s="13" t="s">
@@ -3904,8 +3896,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="39"/>
-      <c r="B109" s="47"/>
+      <c r="A109" s="37"/>
+      <c r="B109" s="44"/>
       <c r="C109" s="6" t="s">
         <v>239</v>
       </c>
@@ -3918,6 +3910,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="B54:B63"/>
+    <mergeCell ref="B64:B73"/>
+    <mergeCell ref="A74:A83"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B74:B77"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="A84:A109"/>
     <mergeCell ref="A2:A22"/>
@@ -3934,12 +3932,6 @@
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="B103:B107"/>
     <mergeCell ref="A45:A73"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="B54:B63"/>
-    <mergeCell ref="B64:B73"/>
-    <mergeCell ref="A74:A83"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B74:B77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
